--- a/research/traditional_assets/database/data/malaysia/malaysia_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/malaysia/malaysia_bank_money_center.xlsx
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.03225</v>
+        <v>0.03985</v>
       </c>
       <c r="E2">
-        <v>0.0325</v>
+        <v>0.04545</v>
       </c>
       <c r="F2">
-        <v>0.064</v>
+        <v>0.102</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,91 +603,91 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.000176353789621677</v>
+        <v>0.0001089313822450864</v>
       </c>
       <c r="J2">
-        <v>0.0001406040751813082</v>
+        <v>7.943086109624242e-05</v>
       </c>
       <c r="K2">
-        <v>5279.599999999999</v>
+        <v>6765.4</v>
       </c>
       <c r="L2">
-        <v>0.2963553390101655</v>
+        <v>0.3792200803798143</v>
       </c>
       <c r="M2">
-        <v>2839.55</v>
+        <v>2909.13</v>
       </c>
       <c r="N2">
-        <v>0.03480587135721509</v>
+        <v>0.03460012416952708</v>
       </c>
       <c r="O2">
-        <v>0.5378343056292144</v>
+        <v>0.4300011824873622</v>
       </c>
       <c r="P2">
-        <v>2836.1</v>
+        <v>2902.3</v>
       </c>
       <c r="Q2">
-        <v>0.03476358287622958</v>
+        <v>0.03451889065707564</v>
       </c>
       <c r="R2">
-        <v>0.5371808470338663</v>
+        <v>0.4289916339019128</v>
       </c>
       <c r="S2">
-        <v>3.45</v>
+        <v>6.829999999999998</v>
       </c>
       <c r="T2">
-        <v>0.001214981247028579</v>
+        <v>0.002347780951693461</v>
       </c>
       <c r="U2">
-        <v>43403.1</v>
+        <v>34743.6</v>
       </c>
       <c r="V2">
-        <v>0.5320148316121717</v>
+        <v>0.4132276227244506</v>
       </c>
       <c r="W2">
-        <v>0.08935370892180991</v>
+        <v>0.08969269291460279</v>
       </c>
       <c r="X2">
-        <v>0.06037960785850646</v>
+        <v>0.09691216404000087</v>
       </c>
       <c r="Y2">
-        <v>0.02897410106330345</v>
+        <v>-0.007219471125398086</v>
       </c>
       <c r="Z2">
-        <v>0.2026084973775053</v>
+        <v>0.2254302725568961</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.0471586587806022</v>
+        <v>0.07411685014303615</v>
       </c>
       <c r="AC2">
-        <v>-0.0471586587806022</v>
+        <v>-0.07411685014303615</v>
       </c>
       <c r="AD2">
-        <v>52068.1</v>
+        <v>61568.3</v>
       </c>
       <c r="AE2">
-        <v>7.591198012554309</v>
+        <v>3.783157306664924</v>
       </c>
       <c r="AF2">
-        <v>52075.69119801256</v>
+        <v>61572.08315730666</v>
       </c>
       <c r="AG2">
-        <v>8672.59119801256</v>
+        <v>26828.48315730666</v>
       </c>
       <c r="AH2">
-        <v>0.3896184044632418</v>
+        <v>0.4227380319995283</v>
       </c>
       <c r="AI2">
-        <v>0.4009959098390996</v>
+        <v>0.4585624022933492</v>
       </c>
       <c r="AJ2">
-        <v>0.09608977269753768</v>
+        <v>0.2419005386631086</v>
       </c>
       <c r="AK2">
-        <v>0.1003043167800476</v>
+        <v>0.2695561035579538</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -696,10 +696,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>11173.41201716738</v>
+        <v>22803.07407407407</v>
       </c>
       <c r="AP2">
-        <v>1861.071072534884</v>
+        <v>9936.475243446912</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +710,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Hong Leong Bank Berhad (KLSE:HLBANK)</t>
+          <t>AFFIN Bank Berhad (KLSE:AFFIN)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0301</v>
+        <v>0.101</v>
       </c>
       <c r="E3">
-        <v>0.09</v>
+        <v>0.293</v>
       </c>
       <c r="F3">
-        <v>0.04099999999999999</v>
+        <v>0.004</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -740,28 +740,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>714.9</v>
+        <v>294.5</v>
       </c>
       <c r="L3">
-        <v>0.6134374463703449</v>
+        <v>0.6544444444444445</v>
       </c>
       <c r="M3">
-        <v>170.3</v>
+        <v>57.1</v>
       </c>
       <c r="N3">
-        <v>0.0186087678657284</v>
+        <v>0.05417971344529841</v>
       </c>
       <c r="O3">
-        <v>0.2382151349839139</v>
+        <v>0.1938879456706282</v>
       </c>
       <c r="P3">
-        <v>170.3</v>
+        <v>57.1</v>
       </c>
       <c r="Q3">
-        <v>0.0186087678657284</v>
+        <v>0.05417971344529841</v>
       </c>
       <c r="R3">
-        <v>0.2382151349839139</v>
+        <v>0.1938879456706282</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,55 +770,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1708.7</v>
+        <v>816</v>
       </c>
       <c r="V3">
-        <v>0.18671052056471</v>
+        <v>0.7742670082550526</v>
       </c>
       <c r="W3">
-        <v>0.1058499533602807</v>
+        <v>0.1289461009676431</v>
       </c>
       <c r="X3">
-        <v>0.05135709765009564</v>
+        <v>0.1144861249279836</v>
       </c>
       <c r="Y3">
-        <v>0.05449285571018509</v>
+        <v>0.01445997603965948</v>
       </c>
       <c r="Z3">
-        <v>0.1656927560958271</v>
+        <v>0.2676818749628219</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.0463425876762709</v>
+        <v>0.07407095755409272</v>
       </c>
       <c r="AC3">
-        <v>-0.0463425876762709</v>
+        <v>-0.07407095755409272</v>
       </c>
       <c r="AD3">
-        <v>2202</v>
+        <v>1579</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>2202</v>
+        <v>1579</v>
       </c>
       <c r="AG3">
-        <v>493.3</v>
+        <v>763</v>
       </c>
       <c r="AH3">
-        <v>0.1939472942502818</v>
+        <v>0.599718941091572</v>
       </c>
       <c r="AI3">
-        <v>0.238329743595294</v>
+        <v>0.4013012427885226</v>
       </c>
       <c r="AJ3">
-        <v>0.05114620161950875</v>
+        <v>0.4199460619736914</v>
       </c>
       <c r="AK3">
-        <v>0.06550606857355323</v>
+        <v>0.2446532208933209</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -835,7 +835,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Public Bank Berhad (KLSE:PBBANK)</t>
+          <t>CIMB Group Holdings Berhad (KLSE:CIMB)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -844,13 +844,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0239</v>
+        <v>0.0298</v>
       </c>
       <c r="E4">
-        <v>0.007820000000000001</v>
+        <v>0.0308</v>
       </c>
       <c r="F4">
-        <v>0.0834</v>
+        <v>0.603</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -865,28 +865,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>1296.8</v>
+        <v>1069.3</v>
       </c>
       <c r="L4">
-        <v>0.49861581051984</v>
+        <v>0.2874771480804387</v>
       </c>
       <c r="M4">
-        <v>951.4</v>
+        <v>76.3</v>
       </c>
       <c r="N4">
-        <v>0.04909083403851313</v>
+        <v>0.005402611380179568</v>
       </c>
       <c r="O4">
-        <v>0.7336520666255398</v>
+        <v>0.0713550921163378</v>
       </c>
       <c r="P4">
-        <v>951.4</v>
+        <v>76.3</v>
       </c>
       <c r="Q4">
-        <v>0.04909083403851313</v>
+        <v>0.005402611380179568</v>
       </c>
       <c r="R4">
-        <v>0.7336520666255398</v>
+        <v>0.0713550921163378</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -895,55 +895,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>5175.7</v>
+        <v>9628</v>
       </c>
       <c r="V4">
-        <v>0.2670584714453778</v>
+        <v>0.6817345002407454</v>
       </c>
       <c r="W4">
-        <v>0.1169584314149914</v>
+        <v>0.07673318837771702</v>
       </c>
       <c r="X4">
-        <v>0.04939146332286262</v>
+        <v>0.1133590631782862</v>
       </c>
       <c r="Y4">
-        <v>0.06756696809212875</v>
+        <v>-0.03662587480056917</v>
       </c>
       <c r="Z4">
-        <v>0.2562617006601636</v>
+        <v>0.1909622038997444</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.04663765785057395</v>
+        <v>0.07407230631220257</v>
       </c>
       <c r="AC4">
-        <v>-0.04663765785057395</v>
+        <v>-0.07407230631220257</v>
       </c>
       <c r="AD4">
-        <v>3027.9</v>
+        <v>20567.6</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>3027.9</v>
+        <v>20567.6</v>
       </c>
       <c r="AG4">
-        <v>-2147.8</v>
+        <v>10939.6</v>
       </c>
       <c r="AH4">
-        <v>0.1351240388606008</v>
+        <v>0.5928902520582063</v>
       </c>
       <c r="AI4">
-        <v>0.2078559513430766</v>
+        <v>0.6021118823388204</v>
       </c>
       <c r="AJ4">
-        <v>-0.1246358645822453</v>
+        <v>0.4364945097037793</v>
       </c>
       <c r="AK4">
-        <v>-0.2286937263086162</v>
+        <v>0.4459482045240531</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -960,7 +960,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Alliance Bank Malaysia Berhad (KLSE:ABMB)</t>
+          <t>AMMB Holdings Berhad (KLSE:AMBANK)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -969,13 +969,13 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.006500000000000001</v>
+        <v>0.0251</v>
       </c>
       <c r="E5">
-        <v>-0.024</v>
+        <v>0.0474</v>
       </c>
       <c r="F5">
-        <v>0.148</v>
+        <v>0.0425</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -990,85 +990,85 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>112.2</v>
+        <v>355</v>
       </c>
       <c r="L5">
-        <v>0.3255004351610096</v>
+        <v>0.3693684320049943</v>
       </c>
       <c r="M5">
-        <v>21.4</v>
+        <v>42.43</v>
       </c>
       <c r="N5">
-        <v>0.02013738590382987</v>
+        <v>0.01356414436878617</v>
       </c>
       <c r="O5">
-        <v>0.1907308377896613</v>
+        <v>0.1195211267605634</v>
       </c>
       <c r="P5">
-        <v>21.4</v>
+        <v>35.6</v>
       </c>
       <c r="Q5">
-        <v>0.02013738590382987</v>
+        <v>0.01138071033534734</v>
       </c>
       <c r="R5">
-        <v>0.1907308377896613</v>
+        <v>0.1002816901408451</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>6.829999999999998</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>0.1609710110770681</v>
       </c>
       <c r="U5">
-        <v>709.4</v>
+        <v>1402.8</v>
       </c>
       <c r="V5">
-        <v>0.6675449327185471</v>
+        <v>0.4484511364726191</v>
       </c>
       <c r="W5">
-        <v>0.0726966437734871</v>
+        <v>0.09207864294236655</v>
       </c>
       <c r="X5">
-        <v>0.05547385739983021</v>
+        <v>0.105739554033871</v>
       </c>
       <c r="Y5">
-        <v>0.01722278637365689</v>
+        <v>-0.01366091109150447</v>
       </c>
       <c r="Z5">
-        <v>0.3255264897535178</v>
+        <v>0.3059756136385343</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.04664868041163295</v>
+        <v>0.07408278917072907</v>
       </c>
       <c r="AC5">
-        <v>-0.04664868041163295</v>
+        <v>-0.07408278917072907</v>
       </c>
       <c r="AD5">
-        <v>443.5</v>
+        <v>3669.4</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>443.5</v>
+        <v>3669.4</v>
       </c>
       <c r="AG5">
-        <v>-265.9</v>
+        <v>2266.6</v>
       </c>
       <c r="AH5">
-        <v>0.2944496082857522</v>
+        <v>0.5398161088635528</v>
       </c>
       <c r="AI5">
-        <v>0.2236623127742196</v>
+        <v>0.4968787661308887</v>
       </c>
       <c r="AJ5">
-        <v>-0.3337098393574296</v>
+        <v>0.4201531132407734</v>
       </c>
       <c r="AK5">
-        <v>-0.2087946603847664</v>
+        <v>0.3788970428444861</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Hong Leong Financial Group Berhad (KLSE:HLFG)</t>
+          <t>Bank Islam Malaysia Berhad (KLSE:BIMB)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1094,10 +1094,13 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0479</v>
+        <v>0.0284</v>
       </c>
       <c r="E6">
-        <v>0.113</v>
+        <v>-0.0493</v>
+      </c>
+      <c r="F6">
+        <v>0.053</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1112,85 +1115,82 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>554.4</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="L6">
-        <v>0.4094534711964549</v>
+        <v>0.2205104621752127</v>
       </c>
       <c r="M6">
-        <v>97.40000000000001</v>
+        <v>-0</v>
       </c>
       <c r="N6">
-        <v>0.02064171576315009</v>
+        <v>-0</v>
       </c>
       <c r="O6">
-        <v>0.1756854256854257</v>
+        <v>-0</v>
       </c>
       <c r="P6">
-        <v>97.40000000000001</v>
+        <v>-0</v>
       </c>
       <c r="Q6">
-        <v>0.02064171576315009</v>
+        <v>-0</v>
       </c>
       <c r="R6">
-        <v>0.1756854256854257</v>
+        <v>-0</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
       <c r="U6">
-        <v>2434.8</v>
+        <v>1654</v>
       </c>
       <c r="V6">
-        <v>0.5160005086254398</v>
+        <v>1.231204406729195</v>
       </c>
       <c r="W6">
-        <v>0.106901139584659</v>
+        <v>0.06173952230734565</v>
       </c>
       <c r="X6">
-        <v>0.05833763523021277</v>
+        <v>0.09830847593669856</v>
       </c>
       <c r="Y6">
-        <v>0.04856350435444621</v>
+        <v>-0.0365689536293529</v>
       </c>
       <c r="Z6">
-        <v>0.2686667857213723</v>
+        <v>0.2569268033319548</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.04682018573412351</v>
+        <v>0.0740960289861463</v>
       </c>
       <c r="AC6">
-        <v>-0.04682018573412351</v>
+        <v>-0.0740960289861463</v>
       </c>
       <c r="AD6">
-        <v>2549.3</v>
+        <v>1204.7</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>2549.3</v>
+        <v>1204.7</v>
       </c>
       <c r="AG6">
-        <v>114.5</v>
+        <v>-449.3</v>
       </c>
       <c r="AH6">
-        <v>0.3507615679907539</v>
+        <v>0.4727836427141792</v>
       </c>
       <c r="AI6">
-        <v>0.2380298786181139</v>
+        <v>0.4513675533907831</v>
       </c>
       <c r="AJ6">
-        <v>0.02369079886615216</v>
+        <v>-0.5025164970361256</v>
       </c>
       <c r="AK6">
-        <v>0.01383652358855375</v>
+        <v>-0.4426600985221674</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AMMB Holdings Berhad (KLSE:AMBANK)</t>
+          <t>Hong Leong Financial Group Berhad (KLSE:HLFG)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1216,10 +1216,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>-0.0239</v>
-      </c>
-      <c r="F7">
-        <v>0.064</v>
+        <v>0.0455</v>
+      </c>
+      <c r="E7">
+        <v>0.09609999999999999</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1234,85 +1234,85 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>-889.7</v>
+        <v>536.5</v>
       </c>
       <c r="L7">
-        <v>-1.084470989761092</v>
+        <v>0.4030803906836964</v>
       </c>
       <c r="M7">
-        <v>3.45</v>
+        <v>108.2</v>
       </c>
       <c r="N7">
-        <v>0.001369156282244622</v>
+        <v>0.0224695767745151</v>
       </c>
       <c r="O7">
-        <v>-0.00387771158817579</v>
+        <v>0.2016775396085741</v>
       </c>
       <c r="P7">
-        <v>-0</v>
+        <v>108.2</v>
       </c>
       <c r="Q7">
-        <v>-0</v>
+        <v>0.0224695767745151</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>0.2016775396085741</v>
       </c>
       <c r="S7">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="T7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U7">
-        <v>2485.8</v>
+        <v>3249.2</v>
       </c>
       <c r="V7">
-        <v>0.9865068656242559</v>
+        <v>0.6747518378535532</v>
       </c>
       <c r="W7">
-        <v>-0.1912387421275498</v>
+        <v>0.09749404859256029</v>
       </c>
       <c r="X7">
-        <v>0.06212933648236586</v>
+        <v>0.09613892854225449</v>
       </c>
       <c r="Y7">
-        <v>-0.2533680786099157</v>
+        <v>0.001355120050305803</v>
       </c>
       <c r="Z7">
-        <v>0.1483812624344366</v>
+        <v>0.2640349137075977</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.04700916821650931</v>
+        <v>0.07410065418550819</v>
       </c>
       <c r="AC7">
-        <v>-0.04700916821650931</v>
+        <v>-0.07410065418550819</v>
       </c>
       <c r="AD7">
-        <v>1771.5</v>
+        <v>3929.8</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>1771.5</v>
+        <v>3929.8</v>
       </c>
       <c r="AG7">
-        <v>-714.3000000000002</v>
+        <v>680.6000000000004</v>
       </c>
       <c r="AH7">
-        <v>0.4128119684011838</v>
+        <v>0.4493665096281388</v>
       </c>
       <c r="AI7">
-        <v>0.3031832962519254</v>
+        <v>0.3343258694616484</v>
       </c>
       <c r="AJ7">
-        <v>-0.3956244807532541</v>
+        <v>0.1238355167394469</v>
       </c>
       <c r="AK7">
-        <v>-0.2127665912069582</v>
+        <v>0.08002163382401357</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AFFIN Bank Berhad (KLSE:AFFIN)</t>
+          <t>Alliance Bank Malaysia Berhad (KLSE:ABMB)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1338,13 +1338,13 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.07429999999999999</v>
+        <v>0.0464</v>
       </c>
       <c r="E8">
-        <v>-0.066</v>
+        <v>0.0435</v>
       </c>
       <c r="F8">
-        <v>0.2</v>
+        <v>0.188</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1359,28 +1359,28 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>74.3</v>
+        <v>134.4</v>
       </c>
       <c r="L8">
-        <v>0.172110261755849</v>
+        <v>0.3549920760697306</v>
       </c>
       <c r="M8">
-        <v>17.4</v>
+        <v>61.6</v>
       </c>
       <c r="N8">
-        <v>0.01973012813244132</v>
+        <v>0.04748689485044712</v>
       </c>
       <c r="O8">
-        <v>0.234185733512786</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="P8">
-        <v>17.4</v>
+        <v>61.6</v>
       </c>
       <c r="Q8">
-        <v>0.01973012813244132</v>
+        <v>0.04748689485044712</v>
       </c>
       <c r="R8">
-        <v>0.234185733512786</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1389,55 +1389,55 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>1524.3</v>
+        <v>928.8</v>
       </c>
       <c r="V8">
-        <v>1.728427259326454</v>
+        <v>0.7160037002775208</v>
       </c>
       <c r="W8">
-        <v>0.03222448714056469</v>
+        <v>0.08730674288683903</v>
       </c>
       <c r="X8">
-        <v>0.07009337371787426</v>
+        <v>0.08492954501657832</v>
       </c>
       <c r="Y8">
-        <v>-0.03786888657730957</v>
+        <v>0.002377197870260708</v>
       </c>
       <c r="Z8">
-        <v>0.3127580960660726</v>
+        <v>0.2972909305064782</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.0473081493446951</v>
+        <v>0.07413304610056409</v>
       </c>
       <c r="AC8">
-        <v>-0.0473081493446951</v>
+        <v>-0.07413304610056409</v>
       </c>
       <c r="AD8">
-        <v>921.5</v>
+        <v>518</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>921.5</v>
+        <v>518</v>
       </c>
       <c r="AG8">
-        <v>-602.8</v>
+        <v>-410.8</v>
       </c>
       <c r="AH8">
-        <v>0.5109792613951425</v>
+        <v>0.2853680035257823</v>
       </c>
       <c r="AI8">
-        <v>0.2865717128996144</v>
+        <v>0.2707364239795119</v>
       </c>
       <c r="AJ8">
-        <v>-2.159799355069867</v>
+        <v>-0.4634476534296028</v>
       </c>
       <c r="AK8">
-        <v>-0.3564122272807899</v>
+        <v>-0.4172676485525647</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CIMB Group Holdings Berhad (KLSE:CIMB)</t>
+          <t>Hong Leong Bank Berhad (KLSE:HLBANK)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1463,13 +1463,13 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.0368</v>
+        <v>0.04480000000000001</v>
       </c>
       <c r="E9">
-        <v>0.006710000000000001</v>
+        <v>0.0877</v>
       </c>
       <c r="F9">
-        <v>0.023</v>
+        <v>0.095</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1484,28 +1484,28 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>874.1</v>
+        <v>734.3</v>
       </c>
       <c r="L9">
-        <v>0.2268562975266669</v>
+        <v>0.6150946557212263</v>
       </c>
       <c r="M9">
-        <v>26.4</v>
+        <v>234.5</v>
       </c>
       <c r="N9">
-        <v>0.001974540395805597</v>
+        <v>0.02438872190616842</v>
       </c>
       <c r="O9">
-        <v>0.03020249399382222</v>
+        <v>0.3193517635843661</v>
       </c>
       <c r="P9">
-        <v>26.4</v>
+        <v>234.5</v>
       </c>
       <c r="Q9">
-        <v>0.001974540395805597</v>
+        <v>0.02438872190616842</v>
       </c>
       <c r="R9">
-        <v>0.03020249399382222</v>
+        <v>0.3193517635843661</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1514,55 +1514,55 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>10437.9</v>
+        <v>2700.9</v>
       </c>
       <c r="V9">
-        <v>0.7806839089916381</v>
+        <v>0.280901914696675</v>
       </c>
       <c r="W9">
-        <v>0.06596632630728942</v>
+        <v>0.1043439955664815</v>
       </c>
       <c r="X9">
-        <v>0.07627979282515429</v>
+        <v>0.08352303349290539</v>
       </c>
       <c r="Y9">
-        <v>-0.01031346651786487</v>
+        <v>0.02082096207357606</v>
       </c>
       <c r="Z9">
-        <v>0.1977540891897579</v>
+        <v>0.1683139002072553</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.0474793371999212</v>
+        <v>0.07413852583162765</v>
       </c>
       <c r="AC9">
-        <v>-0.0474793371999212</v>
+        <v>-0.07413852583162765</v>
       </c>
       <c r="AD9">
-        <v>17521.2</v>
+        <v>3336.7</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>17521.2</v>
+        <v>3336.7</v>
       </c>
       <c r="AG9">
-        <v>7083.300000000001</v>
+        <v>635.7999999999997</v>
       </c>
       <c r="AH9">
-        <v>0.5671869840797115</v>
+        <v>0.257624422860143</v>
       </c>
       <c r="AI9">
-        <v>0.5518609859115003</v>
+        <v>0.3322512870044908</v>
       </c>
       <c r="AJ9">
-        <v>0.3463123670765395</v>
+        <v>0.06202382229852986</v>
       </c>
       <c r="AK9">
-        <v>0.3323714068526704</v>
+        <v>0.08660001634476557</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RHB Bank Berhad (KLSE:RHBBANK)</t>
+          <t>Public Bank Berhad (KLSE:PBBANK)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1588,13 +1588,13 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.0344</v>
+        <v>0.0349</v>
       </c>
       <c r="E10">
-        <v>0.0634</v>
+        <v>0.0114</v>
       </c>
       <c r="F10">
-        <v>0.063</v>
+        <v>0.116</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1603,34 +1603,34 @@
         <v>0</v>
       </c>
       <c r="I10">
-        <v>0.001909884740114978</v>
+        <v>0</v>
       </c>
       <c r="J10">
-        <v>0.001460042082363015</v>
+        <v>0</v>
       </c>
       <c r="K10">
-        <v>580</v>
+        <v>1245.1</v>
       </c>
       <c r="L10">
-        <v>0.3525835866261398</v>
+        <v>0.4724519996964407</v>
       </c>
       <c r="M10">
-        <v>104.9</v>
+        <v>655.7</v>
       </c>
       <c r="N10">
-        <v>0.01964566634204809</v>
+        <v>0.03424950900505621</v>
       </c>
       <c r="O10">
-        <v>0.1808620689655173</v>
+        <v>0.5266243675206811</v>
       </c>
       <c r="P10">
-        <v>104.9</v>
+        <v>655.7</v>
       </c>
       <c r="Q10">
-        <v>0.01964566634204809</v>
+        <v>0.03424950900505621</v>
       </c>
       <c r="R10">
-        <v>0.1808620689655173</v>
+        <v>0.5266243675206811</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1639,67 +1639,61 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>3955.2</v>
+        <v>2897.9</v>
       </c>
       <c r="V10">
-        <v>0.7407296426698629</v>
+        <v>0.1513674731519786</v>
       </c>
       <c r="W10">
-        <v>0.08831501050644092</v>
+        <v>0.1108233199821985</v>
       </c>
       <c r="X10">
-        <v>0.05862987923464705</v>
+        <v>0.07815072155350847</v>
       </c>
       <c r="Y10">
-        <v>0.02968513127179386</v>
+        <v>0.03267259842869001</v>
       </c>
       <c r="Z10">
-        <v>0.2731699969177308</v>
+        <v>0.2900123250286117</v>
       </c>
       <c r="AA10">
-        <v>0.0003988396911388621</v>
+        <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.04839296184595534</v>
+        <v>0.07491530671696441</v>
       </c>
       <c r="AC10">
-        <v>-0.04799412215481648</v>
+        <v>-0.07491530671696441</v>
       </c>
       <c r="AD10">
-        <v>2944.2</v>
+        <v>2819.7</v>
       </c>
       <c r="AE10">
-        <v>7.591198012554309</v>
+        <v>0</v>
       </c>
       <c r="AF10">
-        <v>2951.791198012554</v>
+        <v>2819.7</v>
       </c>
       <c r="AG10">
-        <v>-1003.408801987446</v>
+        <v>-78.20000000000027</v>
       </c>
       <c r="AH10">
-        <v>0.3560067457340692</v>
+        <v>0.1283753329235812</v>
       </c>
       <c r="AI10">
-        <v>0.3068297141174232</v>
+        <v>0.2056209026405408</v>
       </c>
       <c r="AJ10">
-        <v>-0.2314032652543889</v>
+        <v>-0.004101412942003308</v>
       </c>
       <c r="AK10">
-        <v>-0.1771213855020489</v>
+        <v>-0.007230564390857338</v>
       </c>
       <c r="AL10">
         <v>0</v>
       </c>
       <c r="AM10">
         <v>0</v>
-      </c>
-      <c r="AN10">
-        <v>631.8025751072961</v>
-      </c>
-      <c r="AP10">
-        <v>-215.3237772505248</v>
       </c>
     </row>
     <row r="11">
@@ -1710,7 +1704,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Malayan Banking Berhad (KLSE:MAYBANK)</t>
+          <t>RHB Bank Berhad (KLSE:RHBBANK)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1719,13 +1713,13 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.025</v>
+        <v>0.07690000000000001</v>
       </c>
       <c r="E11">
-        <v>0.0466</v>
+        <v>0.0795</v>
       </c>
       <c r="F11">
-        <v>0.033</v>
+        <v>0.152</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1734,34 +1728,34 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>0.001201018811363337</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>0.0007971708292950646</v>
       </c>
       <c r="K11">
-        <v>1811.5</v>
+        <v>552.3</v>
       </c>
       <c r="L11">
-        <v>0.3543345591111807</v>
+        <v>0.341326246832705</v>
       </c>
       <c r="M11">
-        <v>1413.5</v>
+        <v>202</v>
       </c>
       <c r="N11">
-        <v>0.05973460677006297</v>
+        <v>0.03597698897536823</v>
       </c>
       <c r="O11">
-        <v>0.7802925752139112</v>
+        <v>0.3657432554770958</v>
       </c>
       <c r="P11">
-        <v>1413.5</v>
+        <v>202</v>
       </c>
       <c r="Q11">
-        <v>0.05973460677006297</v>
+        <v>0.03597698897536823</v>
       </c>
       <c r="R11">
-        <v>0.7802925752139112</v>
+        <v>0.3657432554770958</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -1770,61 +1764,67 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>13942.2</v>
+        <v>3223.2</v>
       </c>
       <c r="V11">
-        <v>0.589198326501289</v>
+        <v>0.5740645092346875</v>
       </c>
       <c r="W11">
-        <v>0.09039240733717889</v>
+        <v>0.08292170257488175</v>
       </c>
       <c r="X11">
-        <v>0.06496721413418283</v>
+        <v>0.08870721300270243</v>
       </c>
       <c r="Y11">
-        <v>0.02542519320299606</v>
+        <v>-0.005785510427820675</v>
       </c>
       <c r="Z11">
-        <v>0.169725379793902</v>
+        <v>0.3224152530219445</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>0.0002570200346288816</v>
       </c>
       <c r="AB11">
-        <v>0.04871490514016268</v>
+        <v>0.07667782078017474</v>
       </c>
       <c r="AC11">
-        <v>-0.04871490514016268</v>
+        <v>-0.07642080074554586</v>
       </c>
       <c r="AD11">
-        <v>19518.5</v>
+        <v>3026.9</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>3.783157306664924</v>
       </c>
       <c r="AF11">
-        <v>19518.5</v>
+        <v>3030.683157306665</v>
       </c>
       <c r="AG11">
-        <v>5576.299999999999</v>
+        <v>-192.5168426933346</v>
       </c>
       <c r="AH11">
-        <v>0.4520106990262033</v>
+        <v>0.3505551000067911</v>
       </c>
       <c r="AI11">
-        <v>0.4853368277618086</v>
+        <v>0.3340964122441195</v>
       </c>
       <c r="AJ11">
-        <v>0.1907124999572493</v>
+        <v>-0.03550541121686539</v>
       </c>
       <c r="AK11">
-        <v>0.2122348159030532</v>
+        <v>-0.03291964862927808</v>
       </c>
       <c r="AL11">
         <v>0</v>
       </c>
       <c r="AM11">
         <v>0</v>
+      </c>
+      <c r="AN11">
+        <v>1121.074074074074</v>
+      </c>
+      <c r="AP11">
+        <v>-71.30253433086467</v>
       </c>
     </row>
     <row r="12">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bank Islam Malaysia Berhad (KLSE:BIMB)</t>
+          <t>Malayan Banking Berhad (KLSE:MAYBANK)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1844,13 +1844,13 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.04849999999999999</v>
+        <v>0.0276</v>
       </c>
       <c r="E12">
-        <v>0.0325</v>
+        <v>0.009509999999999999</v>
       </c>
       <c r="F12">
-        <v>0.111</v>
+        <v>0.102</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1865,28 +1865,28 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>151.1</v>
+        <v>1748.1</v>
       </c>
       <c r="L12">
-        <v>0.3098851517637408</v>
+        <v>0.3415725507053812</v>
       </c>
       <c r="M12">
-        <v>33.4</v>
+        <v>1471.3</v>
       </c>
       <c r="N12">
-        <v>0.0223456211948886</v>
+        <v>0.0614495973804671</v>
       </c>
       <c r="O12">
-        <v>0.2210456651224355</v>
+        <v>0.8416566557977233</v>
       </c>
       <c r="P12">
-        <v>33.4</v>
+        <v>1471.3</v>
       </c>
       <c r="Q12">
-        <v>0.0223456211948886</v>
+        <v>0.0614495973804671</v>
       </c>
       <c r="R12">
-        <v>0.2210456651224355</v>
+        <v>0.8416566557977233</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -1895,55 +1895,55 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>1029.1</v>
+        <v>8242.799999999999</v>
       </c>
       <c r="V12">
-        <v>0.6884993644209539</v>
+        <v>0.3442647599318386</v>
       </c>
       <c r="W12">
-        <v>0.1025588814226566</v>
+        <v>0.08715921102490974</v>
       </c>
       <c r="X12">
-        <v>0.06396339215039641</v>
+        <v>0.09768539953774726</v>
       </c>
       <c r="Y12">
-        <v>0.03859548927226021</v>
+        <v>-0.01052618851283751</v>
       </c>
       <c r="Z12">
-        <v>0.2310352996920161</v>
+        <v>0.1996590292868094</v>
       </c>
       <c r="AA12">
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.0496439784243634</v>
+        <v>0.07682589827495988</v>
       </c>
       <c r="AC12">
-        <v>-0.0496439784243634</v>
+        <v>-0.07682589827495988</v>
       </c>
       <c r="AD12">
-        <v>1168.5</v>
+        <v>20916.5</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>1168.5</v>
+        <v>20916.5</v>
       </c>
       <c r="AG12">
-        <v>139.4000000000001</v>
+        <v>12673.7</v>
       </c>
       <c r="AH12">
-        <v>0.4387578852508261</v>
+        <v>0.4662648212092368</v>
       </c>
       <c r="AI12">
-        <v>0.4293114850466603</v>
+        <v>0.5278012591629972</v>
       </c>
       <c r="AJ12">
-        <v>0.08530689676274407</v>
+        <v>0.3461161376304384</v>
       </c>
       <c r="AK12">
-        <v>0.08235363620251675</v>
+        <v>0.4037920520475233</v>
       </c>
       <c r="AL12">
         <v>0</v>

--- a/research/traditional_assets/database/data/malaysia/malaysia_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/malaysia/malaysia_bank_money_center.xlsx
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.03985</v>
+        <v>0.03515</v>
       </c>
       <c r="E2">
-        <v>0.04545</v>
+        <v>0.0412</v>
       </c>
       <c r="F2">
-        <v>0.102</v>
+        <v>0.07075000000000001</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,91 +603,91 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.0001089313822450864</v>
+        <v>8.353054435597135e-05</v>
       </c>
       <c r="J2">
-        <v>7.943086109624242e-05</v>
+        <v>6.332486105221861e-05</v>
       </c>
       <c r="K2">
-        <v>6765.4</v>
+        <v>7629.5</v>
       </c>
       <c r="L2">
-        <v>0.3792200803798143</v>
+        <v>0.4043790281546811</v>
       </c>
       <c r="M2">
-        <v>2909.13</v>
+        <v>4287.748</v>
       </c>
       <c r="N2">
-        <v>0.03460012416952708</v>
+        <v>0.0543347842891267</v>
       </c>
       <c r="O2">
-        <v>0.4300011824873622</v>
+        <v>0.5619959368241693</v>
       </c>
       <c r="P2">
-        <v>2902.3</v>
+        <v>4273.828</v>
       </c>
       <c r="Q2">
-        <v>0.03451889065707564</v>
+        <v>0.05415838861538266</v>
       </c>
       <c r="R2">
-        <v>0.4289916339019128</v>
+        <v>0.560171439806016</v>
       </c>
       <c r="S2">
-        <v>6.829999999999998</v>
+        <v>13.92000000000001</v>
       </c>
       <c r="T2">
-        <v>0.002347780951693461</v>
+        <v>0.003246459446777193</v>
       </c>
       <c r="U2">
-        <v>34743.6</v>
+        <v>28169.8</v>
       </c>
       <c r="V2">
-        <v>0.4132276227244506</v>
+        <v>0.3569706070570942</v>
       </c>
       <c r="W2">
-        <v>0.08969269291460279</v>
+        <v>0.1060399850779513</v>
       </c>
       <c r="X2">
-        <v>0.09691216404000087</v>
+        <v>0.08322639212971575</v>
       </c>
       <c r="Y2">
-        <v>-0.007219471125398086</v>
+        <v>0.02281359294823554</v>
       </c>
       <c r="Z2">
-        <v>0.2254302725568961</v>
+        <v>0.2032694498561756</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.07411685014303615</v>
+        <v>0.06351521242825592</v>
       </c>
       <c r="AC2">
-        <v>-0.07411685014303615</v>
+        <v>-0.06351521242825592</v>
       </c>
       <c r="AD2">
-        <v>61568.3</v>
+        <v>72547.39999999999</v>
       </c>
       <c r="AE2">
-        <v>3.783157306664924</v>
+        <v>3.370062567635087</v>
       </c>
       <c r="AF2">
-        <v>61572.08315730666</v>
+        <v>72550.77006256764</v>
       </c>
       <c r="AG2">
-        <v>26828.48315730666</v>
+        <v>44380.97006256763</v>
       </c>
       <c r="AH2">
-        <v>0.4227380319995283</v>
+        <v>0.4789959376729442</v>
       </c>
       <c r="AI2">
-        <v>0.4585624022933492</v>
+        <v>0.4812872784382512</v>
       </c>
       <c r="AJ2">
-        <v>0.2419005386631086</v>
+        <v>0.3599591290675555</v>
       </c>
       <c r="AK2">
-        <v>0.2695561035579538</v>
+        <v>0.3620767711609247</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -696,10 +696,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>22803.07407407407</v>
+        <v>32243.28888888888</v>
       </c>
       <c r="AP2">
-        <v>9936.475243446912</v>
+        <v>19724.87558336339</v>
       </c>
     </row>
     <row r="3">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.101</v>
+        <v>-0.009820000000000001</v>
       </c>
       <c r="E3">
-        <v>0.293</v>
+        <v>-0.0644</v>
       </c>
       <c r="F3">
-        <v>0.004</v>
+        <v>0.399</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -740,85 +740,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>294.5</v>
+        <v>80.8</v>
       </c>
       <c r="L3">
-        <v>0.6544444444444445</v>
+        <v>0.2070202408403792</v>
       </c>
       <c r="M3">
-        <v>57.1</v>
+        <v>7.968</v>
       </c>
       <c r="N3">
-        <v>0.05417971344529841</v>
+        <v>0.007489425697903938</v>
       </c>
       <c r="O3">
-        <v>0.1938879456706282</v>
+        <v>0.09861386138613862</v>
       </c>
       <c r="P3">
-        <v>57.1</v>
+        <v>0.128</v>
       </c>
       <c r="Q3">
-        <v>0.05417971344529841</v>
+        <v>0.0001203120594040793</v>
       </c>
       <c r="R3">
-        <v>0.1938879456706282</v>
+        <v>0.001584158415841584</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>7.84</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.9839357429718876</v>
       </c>
       <c r="U3">
-        <v>816</v>
+        <v>882.8</v>
       </c>
       <c r="V3">
-        <v>0.7742670082550526</v>
+        <v>0.8297772347025095</v>
       </c>
       <c r="W3">
-        <v>0.1289461009676431</v>
+        <v>0.03429978350384175</v>
       </c>
       <c r="X3">
-        <v>0.1144861249279836</v>
+        <v>0.106215860389252</v>
       </c>
       <c r="Y3">
-        <v>0.01445997603965948</v>
+        <v>-0.07191607688541028</v>
       </c>
       <c r="Z3">
-        <v>0.2676818749628219</v>
+        <v>0.125148298970725</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.07407095755409272</v>
+        <v>0.06336472170149826</v>
       </c>
       <c r="AC3">
-        <v>-0.07407095755409272</v>
+        <v>-0.06336472170149826</v>
       </c>
       <c r="AD3">
-        <v>1579</v>
+        <v>2373.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1579</v>
+        <v>2373.7</v>
       </c>
       <c r="AG3">
-        <v>763</v>
+        <v>1490.9</v>
       </c>
       <c r="AH3">
-        <v>0.599718941091572</v>
+        <v>0.6905108215033744</v>
       </c>
       <c r="AI3">
-        <v>0.4013012427885226</v>
+        <v>0.5032543939618801</v>
       </c>
       <c r="AJ3">
-        <v>0.4199460619736914</v>
+        <v>0.583568185376546</v>
       </c>
       <c r="AK3">
-        <v>0.2446532208933209</v>
+        <v>0.3888729492162028</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -844,13 +844,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0298</v>
+        <v>0.0349</v>
       </c>
       <c r="E4">
-        <v>0.0308</v>
+        <v>0.0359</v>
       </c>
       <c r="F4">
-        <v>0.603</v>
+        <v>0.14</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -865,28 +865,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>1069.3</v>
+        <v>1403.8</v>
       </c>
       <c r="L4">
-        <v>0.2874771480804387</v>
+        <v>0.3484066315893974</v>
       </c>
       <c r="M4">
-        <v>76.3</v>
+        <v>391.4</v>
       </c>
       <c r="N4">
-        <v>0.005402611380179568</v>
+        <v>0.02877898854428611</v>
       </c>
       <c r="O4">
-        <v>0.0713550921163378</v>
+        <v>0.2788146459609631</v>
       </c>
       <c r="P4">
-        <v>76.3</v>
+        <v>391.4</v>
       </c>
       <c r="Q4">
-        <v>0.005402611380179568</v>
+        <v>0.02877898854428611</v>
       </c>
       <c r="R4">
-        <v>0.0713550921163378</v>
+        <v>0.2788146459609631</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -895,55 +895,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>9628</v>
+        <v>7928.7</v>
       </c>
       <c r="V4">
-        <v>0.6817345002407454</v>
+        <v>0.582984073763621</v>
       </c>
       <c r="W4">
-        <v>0.07673318837771702</v>
+        <v>0.1054727414798341</v>
       </c>
       <c r="X4">
-        <v>0.1133590631782862</v>
+        <v>0.09550714848514597</v>
       </c>
       <c r="Y4">
-        <v>-0.03662587480056917</v>
+        <v>0.009965592994688133</v>
       </c>
       <c r="Z4">
-        <v>0.1909622038997444</v>
+        <v>0.1763634771951327</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.07407230631220257</v>
+        <v>0.06340678066058318</v>
       </c>
       <c r="AC4">
-        <v>-0.07407230631220257</v>
+        <v>-0.06340678066058318</v>
       </c>
       <c r="AD4">
-        <v>20567.6</v>
+        <v>22681.3</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>20567.6</v>
+        <v>22681.3</v>
       </c>
       <c r="AG4">
-        <v>10939.6</v>
+        <v>14752.6</v>
       </c>
       <c r="AH4">
-        <v>0.5928902520582063</v>
+        <v>0.6251478025991207</v>
       </c>
       <c r="AI4">
-        <v>0.6021118823388204</v>
+        <v>0.6046105576866174</v>
       </c>
       <c r="AJ4">
-        <v>0.4364945097037793</v>
+        <v>0.5203225078299145</v>
       </c>
       <c r="AK4">
-        <v>0.4459482045240531</v>
+        <v>0.4986479726349661</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -969,13 +969,13 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0251</v>
+        <v>0.00876</v>
       </c>
       <c r="E5">
-        <v>0.0474</v>
+        <v>0.0837</v>
       </c>
       <c r="F5">
-        <v>0.0425</v>
+        <v>0.034</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -990,85 +990,85 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>355</v>
+        <v>371.9</v>
       </c>
       <c r="L5">
-        <v>0.3693684320049943</v>
+        <v>0.4214164305949008</v>
       </c>
       <c r="M5">
-        <v>42.43</v>
+        <v>134.98</v>
       </c>
       <c r="N5">
-        <v>0.01356414436878617</v>
+        <v>0.04668003873288146</v>
       </c>
       <c r="O5">
-        <v>0.1195211267605634</v>
+        <v>0.3629470287711751</v>
       </c>
       <c r="P5">
-        <v>35.6</v>
+        <v>128.9</v>
       </c>
       <c r="Q5">
-        <v>0.01138071033534734</v>
+        <v>0.04457739659703971</v>
       </c>
       <c r="R5">
-        <v>0.1002816901408451</v>
+        <v>0.3465985479967734</v>
       </c>
       <c r="S5">
-        <v>6.829999999999998</v>
+        <v>6.080000000000013</v>
       </c>
       <c r="T5">
-        <v>0.1609710110770681</v>
+        <v>0.04504371017928591</v>
       </c>
       <c r="U5">
-        <v>1402.8</v>
+        <v>1904.6</v>
       </c>
       <c r="V5">
-        <v>0.4484511364726191</v>
+        <v>0.6586664822243741</v>
       </c>
       <c r="W5">
-        <v>0.09207864294236655</v>
+        <v>0.100099588189379</v>
       </c>
       <c r="X5">
-        <v>0.105739554033871</v>
+        <v>0.09052422879915417</v>
       </c>
       <c r="Y5">
-        <v>-0.01366091109150447</v>
+        <v>0.009575359390224872</v>
       </c>
       <c r="Z5">
-        <v>0.3059756136385343</v>
+        <v>0.1475283772714355</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.07408278917072907</v>
+        <v>0.06343306787639336</v>
       </c>
       <c r="AC5">
-        <v>-0.07408278917072907</v>
+        <v>-0.06343306787639336</v>
       </c>
       <c r="AD5">
-        <v>3669.4</v>
+        <v>4064.3</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>3669.4</v>
+        <v>4064.3</v>
       </c>
       <c r="AG5">
-        <v>2266.6</v>
+        <v>2159.7</v>
       </c>
       <c r="AH5">
-        <v>0.5398161088635528</v>
+        <v>0.5842953463965842</v>
       </c>
       <c r="AI5">
-        <v>0.4968787661308887</v>
+        <v>0.5073652410556013</v>
       </c>
       <c r="AJ5">
-        <v>0.4201531132407734</v>
+        <v>0.4275533031100905</v>
       </c>
       <c r="AK5">
-        <v>0.3788970428444861</v>
+        <v>0.3537012774320341</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bank Islam Malaysia Berhad (KLSE:BIMB)</t>
+          <t>Hong Leong Financial Group Berhad (KLSE:HLFG)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1094,13 +1094,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0284</v>
+        <v>0.0333</v>
       </c>
       <c r="E6">
-        <v>-0.0493</v>
-      </c>
-      <c r="F6">
-        <v>0.053</v>
+        <v>0.079</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1115,82 +1112,85 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>95.90000000000001</v>
+        <v>609.9</v>
       </c>
       <c r="L6">
-        <v>0.2205104621752127</v>
+        <v>0.449944669863519</v>
       </c>
       <c r="M6">
-        <v>-0</v>
+        <v>116.4</v>
       </c>
       <c r="N6">
-        <v>-0</v>
+        <v>0.02864032281875892</v>
       </c>
       <c r="O6">
-        <v>-0</v>
+        <v>0.190850959173635</v>
       </c>
       <c r="P6">
-        <v>-0</v>
+        <v>116.4</v>
       </c>
       <c r="Q6">
-        <v>-0</v>
+        <v>0.02864032281875892</v>
       </c>
       <c r="R6">
-        <v>-0</v>
+        <v>0.190850959173635</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
       <c r="U6">
-        <v>1654</v>
+        <v>1998.9</v>
       </c>
       <c r="V6">
-        <v>1.231204406729195</v>
+        <v>0.4918311106736873</v>
       </c>
       <c r="W6">
-        <v>0.06173952230734565</v>
+        <v>0.1153039039606768</v>
       </c>
       <c r="X6">
-        <v>0.09830847593669856</v>
+        <v>0.08466132443058801</v>
       </c>
       <c r="Y6">
-        <v>-0.0365689536293529</v>
+        <v>0.03064257953008881</v>
       </c>
       <c r="Z6">
-        <v>0.2569268033319548</v>
+        <v>0.2486517224933045</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.0740960289861463</v>
+        <v>0.06347241346399628</v>
       </c>
       <c r="AC6">
-        <v>-0.0740960289861463</v>
+        <v>-0.06347241346399628</v>
       </c>
       <c r="AD6">
-        <v>1204.7</v>
+        <v>4458.8</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>1204.7</v>
+        <v>4458.8</v>
       </c>
       <c r="AG6">
-        <v>-449.3</v>
+        <v>2459.9</v>
       </c>
       <c r="AH6">
-        <v>0.4727836427141792</v>
+        <v>0.523149125894638</v>
       </c>
       <c r="AI6">
-        <v>0.4513675533907831</v>
+        <v>0.3403742070429094</v>
       </c>
       <c r="AJ6">
-        <v>-0.5025164970361256</v>
+        <v>0.3770481752272344</v>
       </c>
       <c r="AK6">
-        <v>-0.4426600985221674</v>
+        <v>0.2215966416834823</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Hong Leong Financial Group Berhad (KLSE:HLFG)</t>
+          <t>Bank Islam Malaysia Berhad (KLSE:BIMB)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1216,10 +1216,13 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0455</v>
+        <v>0.0399</v>
       </c>
       <c r="E7">
-        <v>0.09609999999999999</v>
+        <v>-0.0223</v>
+      </c>
+      <c r="F7">
+        <v>0.05</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1234,28 +1237,28 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>536.5</v>
+        <v>110.9</v>
       </c>
       <c r="L7">
-        <v>0.4030803906836964</v>
+        <v>0.2314756835733667</v>
       </c>
       <c r="M7">
-        <v>108.2</v>
+        <v>54.5</v>
       </c>
       <c r="N7">
-        <v>0.0224695767745151</v>
+        <v>0.04991299569557651</v>
       </c>
       <c r="O7">
-        <v>0.2016775396085741</v>
+        <v>0.4914337240757439</v>
       </c>
       <c r="P7">
-        <v>108.2</v>
+        <v>54.5</v>
       </c>
       <c r="Q7">
-        <v>0.0224695767745151</v>
+        <v>0.04991299569557651</v>
       </c>
       <c r="R7">
-        <v>0.2016775396085741</v>
+        <v>0.4914337240757439</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1264,55 +1267,55 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>3249.2</v>
+        <v>511.6</v>
       </c>
       <c r="V7">
-        <v>0.6747518378535532</v>
+        <v>0.4685410751900357</v>
       </c>
       <c r="W7">
-        <v>0.09749404859256029</v>
+        <v>0.07573584647954655</v>
       </c>
       <c r="X7">
-        <v>0.09613892854225449</v>
+        <v>0.08201344543107547</v>
       </c>
       <c r="Y7">
-        <v>0.001355120050305803</v>
+        <v>-0.00627759895152892</v>
       </c>
       <c r="Z7">
-        <v>0.2640349137075977</v>
+        <v>0.5346501506528291</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.07410065418550819</v>
+        <v>0.06349424742764896</v>
       </c>
       <c r="AC7">
-        <v>-0.07410065418550819</v>
+        <v>-0.06349424742764896</v>
       </c>
       <c r="AD7">
-        <v>3929.8</v>
+        <v>1045.8</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>3929.8</v>
+        <v>1045.8</v>
       </c>
       <c r="AG7">
-        <v>680.6000000000004</v>
+        <v>534.1999999999999</v>
       </c>
       <c r="AH7">
-        <v>0.4493665096281388</v>
+        <v>0.4892173831688263</v>
       </c>
       <c r="AI7">
-        <v>0.3343258694616484</v>
+        <v>0.3970990279465371</v>
       </c>
       <c r="AJ7">
-        <v>0.1238355167394469</v>
+        <v>0.3285160814218068</v>
       </c>
       <c r="AK7">
-        <v>0.08002163382401357</v>
+        <v>0.2517436380772856</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1338,13 +1341,13 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.0464</v>
+        <v>0.0354</v>
       </c>
       <c r="E8">
-        <v>0.0435</v>
+        <v>0.04650000000000001</v>
       </c>
       <c r="F8">
-        <v>0.188</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1359,28 +1362,28 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>134.4</v>
+        <v>137</v>
       </c>
       <c r="L8">
-        <v>0.3549920760697306</v>
+        <v>0.3593913955928646</v>
       </c>
       <c r="M8">
-        <v>61.6</v>
+        <v>72.5</v>
       </c>
       <c r="N8">
-        <v>0.04748689485044712</v>
+        <v>0.06337412587412587</v>
       </c>
       <c r="O8">
-        <v>0.4583333333333333</v>
+        <v>0.5291970802919708</v>
       </c>
       <c r="P8">
-        <v>61.6</v>
+        <v>72.5</v>
       </c>
       <c r="Q8">
-        <v>0.04748689485044712</v>
+        <v>0.06337412587412587</v>
       </c>
       <c r="R8">
-        <v>0.4583333333333333</v>
+        <v>0.5291970802919708</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1389,55 +1392,55 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>928.8</v>
+        <v>583.1</v>
       </c>
       <c r="V8">
-        <v>0.7160037002775208</v>
+        <v>0.5097027972027972</v>
       </c>
       <c r="W8">
-        <v>0.08730674288683903</v>
+        <v>0.0981867698702788</v>
       </c>
       <c r="X8">
-        <v>0.08492954501657832</v>
+        <v>0.07780335108366868</v>
       </c>
       <c r="Y8">
-        <v>0.002377197870260708</v>
+        <v>0.02038341878661012</v>
       </c>
       <c r="Z8">
-        <v>0.2972909305064782</v>
+        <v>0.387201625190452</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.07413304610056409</v>
+        <v>0.06353617742886286</v>
       </c>
       <c r="AC8">
-        <v>-0.07413304610056409</v>
+        <v>-0.06353617742886286</v>
       </c>
       <c r="AD8">
-        <v>518</v>
+        <v>842.3</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>518</v>
+        <v>842.3</v>
       </c>
       <c r="AG8">
-        <v>-410.8</v>
+        <v>259.1999999999999</v>
       </c>
       <c r="AH8">
-        <v>0.2853680035257823</v>
+        <v>0.4240547752101898</v>
       </c>
       <c r="AI8">
-        <v>0.2707364239795119</v>
+        <v>0.3637973480758432</v>
       </c>
       <c r="AJ8">
-        <v>-0.4634476534296028</v>
+        <v>0.1847206385404789</v>
       </c>
       <c r="AK8">
-        <v>-0.4172676485525647</v>
+        <v>0.1496363006581226</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1463,13 +1466,13 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.04480000000000001</v>
+        <v>0.0268</v>
       </c>
       <c r="E9">
-        <v>0.0877</v>
+        <v>0.07400000000000001</v>
       </c>
       <c r="F9">
-        <v>0.095</v>
+        <v>0.05400000000000001</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1484,28 +1487,28 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>734.3</v>
+        <v>823.6</v>
       </c>
       <c r="L9">
-        <v>0.6150946557212263</v>
+        <v>0.696372706518982</v>
       </c>
       <c r="M9">
-        <v>234.5</v>
+        <v>253.1</v>
       </c>
       <c r="N9">
-        <v>0.02438872190616842</v>
+        <v>0.02997998175852552</v>
       </c>
       <c r="O9">
-        <v>0.3193517635843661</v>
+        <v>0.3073093734822729</v>
       </c>
       <c r="P9">
-        <v>234.5</v>
+        <v>253.1</v>
       </c>
       <c r="Q9">
-        <v>0.02438872190616842</v>
+        <v>0.02997998175852552</v>
       </c>
       <c r="R9">
-        <v>0.3193517635843661</v>
+        <v>0.3073093734822729</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1514,55 +1517,55 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>2700.9</v>
+        <v>1714.9</v>
       </c>
       <c r="V9">
-        <v>0.280901914696675</v>
+        <v>0.2031318479561257</v>
       </c>
       <c r="W9">
-        <v>0.1043439955664815</v>
+        <v>0.1228153892036982</v>
       </c>
       <c r="X9">
-        <v>0.08352303349290539</v>
+        <v>0.07266104060401066</v>
       </c>
       <c r="Y9">
-        <v>0.02082096207357606</v>
+        <v>0.05015434859968752</v>
       </c>
       <c r="Z9">
-        <v>0.1683139002072553</v>
+        <v>0.1702265465327154</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.07413852583162765</v>
+        <v>0.06360458471982543</v>
       </c>
       <c r="AC9">
-        <v>-0.07413852583162765</v>
+        <v>-0.06360458471982543</v>
       </c>
       <c r="AD9">
-        <v>3336.7</v>
+        <v>3931.8</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>3336.7</v>
+        <v>3931.8</v>
       </c>
       <c r="AG9">
-        <v>635.7999999999997</v>
+        <v>2216.9</v>
       </c>
       <c r="AH9">
-        <v>0.257624422860143</v>
+        <v>0.3177443207990885</v>
       </c>
       <c r="AI9">
-        <v>0.3322512870044908</v>
+        <v>0.3506184289141155</v>
       </c>
       <c r="AJ9">
-        <v>0.06202382229852986</v>
+        <v>0.2079799609726809</v>
       </c>
       <c r="AK9">
-        <v>0.08660001634476557</v>
+        <v>0.233382461311717</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1588,13 +1591,13 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.0349</v>
+        <v>0.044</v>
       </c>
       <c r="E10">
-        <v>0.0114</v>
+        <v>0.0354</v>
       </c>
       <c r="F10">
-        <v>0.116</v>
+        <v>0.07200000000000001</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1609,28 +1612,28 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>1245.1</v>
+        <v>1437.2</v>
       </c>
       <c r="L10">
-        <v>0.4724519996964407</v>
+        <v>0.5065557591992106</v>
       </c>
       <c r="M10">
-        <v>655.7</v>
+        <v>744.2</v>
       </c>
       <c r="N10">
-        <v>0.03424950900505621</v>
+        <v>0.04099846297081848</v>
       </c>
       <c r="O10">
-        <v>0.5266243675206811</v>
+        <v>0.517812413025327</v>
       </c>
       <c r="P10">
-        <v>655.7</v>
+        <v>744.2</v>
       </c>
       <c r="Q10">
-        <v>0.03424950900505621</v>
+        <v>0.04099846297081848</v>
       </c>
       <c r="R10">
-        <v>0.5266243675206811</v>
+        <v>0.517812413025327</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1639,55 +1642,55 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>2897.9</v>
+        <v>2052.6</v>
       </c>
       <c r="V10">
-        <v>0.1513674731519786</v>
+        <v>0.1130790716123381</v>
       </c>
       <c r="W10">
-        <v>0.1108233199821985</v>
+        <v>0.1357219079636992</v>
       </c>
       <c r="X10">
-        <v>0.07815072155350847</v>
+        <v>0.06723662315856165</v>
       </c>
       <c r="Y10">
-        <v>0.03267259842869001</v>
+        <v>0.06848528480513756</v>
       </c>
       <c r="Z10">
-        <v>0.2900123250286117</v>
+        <v>0.2699241753955342</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.07491530671696441</v>
+        <v>0.0643855889586472</v>
       </c>
       <c r="AC10">
-        <v>-0.07491530671696441</v>
+        <v>-0.0643855889586472</v>
       </c>
       <c r="AD10">
-        <v>2819.7</v>
+        <v>3273.4</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>2819.7</v>
+        <v>3273.4</v>
       </c>
       <c r="AG10">
-        <v>-78.20000000000027</v>
+        <v>1220.8</v>
       </c>
       <c r="AH10">
-        <v>0.1283753329235812</v>
+        <v>0.1527819913840179</v>
       </c>
       <c r="AI10">
-        <v>0.2056209026405408</v>
+        <v>0.219451204387147</v>
       </c>
       <c r="AJ10">
-        <v>-0.004101412942003308</v>
+        <v>0.0630165129279863</v>
       </c>
       <c r="AK10">
-        <v>-0.007230564390857338</v>
+        <v>0.09490271072863951</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1704,7 +1707,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>RHB Bank Berhad (KLSE:RHBBANK)</t>
+          <t>Malayan Banking Berhad (KLSE:MAYBANK)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1713,13 +1716,13 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.07690000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="E11">
-        <v>0.0795</v>
+        <v>0.0358</v>
       </c>
       <c r="F11">
-        <v>0.152</v>
+        <v>0.0848</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1728,34 +1731,34 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>0.001201018811363337</v>
+        <v>0</v>
       </c>
       <c r="J11">
-        <v>0.0007971708292950646</v>
+        <v>0</v>
       </c>
       <c r="K11">
-        <v>552.3</v>
+        <v>2011.1</v>
       </c>
       <c r="L11">
-        <v>0.341326246832705</v>
+        <v>0.3578597103099754</v>
       </c>
       <c r="M11">
-        <v>202</v>
+        <v>2228.7</v>
       </c>
       <c r="N11">
-        <v>0.03597698897536823</v>
+        <v>0.0953605490494752</v>
       </c>
       <c r="O11">
-        <v>0.3657432554770958</v>
+        <v>1.108199492814877</v>
       </c>
       <c r="P11">
-        <v>202</v>
+        <v>2228.7</v>
       </c>
       <c r="Q11">
-        <v>0.03597698897536823</v>
+        <v>0.0953605490494752</v>
       </c>
       <c r="R11">
-        <v>0.3657432554770958</v>
+        <v>1.108199492814877</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -1764,67 +1767,61 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>3223.2</v>
+        <v>7890.4</v>
       </c>
       <c r="V11">
-        <v>0.5740645092346875</v>
+        <v>0.337610659227343</v>
       </c>
       <c r="W11">
-        <v>0.08292170257488175</v>
+        <v>0.1108826059149152</v>
       </c>
       <c r="X11">
-        <v>0.08870721300270243</v>
+        <v>0.08443933882835604</v>
       </c>
       <c r="Y11">
-        <v>-0.005785510427820675</v>
+        <v>0.02644326708655916</v>
       </c>
       <c r="Z11">
-        <v>0.3224152530219445</v>
+        <v>0.1823964895540215</v>
       </c>
       <c r="AA11">
-        <v>0.0002570200346288816</v>
+        <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.07667782078017474</v>
+        <v>0.06577314810843811</v>
       </c>
       <c r="AC11">
-        <v>-0.07642080074554586</v>
+        <v>-0.06577314810843811</v>
       </c>
       <c r="AD11">
-        <v>3026.9</v>
+        <v>25367.5</v>
       </c>
       <c r="AE11">
-        <v>3.783157306664924</v>
+        <v>0</v>
       </c>
       <c r="AF11">
-        <v>3030.683157306665</v>
+        <v>25367.5</v>
       </c>
       <c r="AG11">
-        <v>-192.5168426933346</v>
+        <v>17477.1</v>
       </c>
       <c r="AH11">
-        <v>0.3505551000067911</v>
+        <v>0.5204785509696587</v>
       </c>
       <c r="AI11">
-        <v>0.3340964122441195</v>
+        <v>0.5583496577377677</v>
       </c>
       <c r="AJ11">
-        <v>-0.03550541121686539</v>
+        <v>0.4278527433143036</v>
       </c>
       <c r="AK11">
-        <v>-0.03291964862927808</v>
+        <v>0.4655271611449393</v>
       </c>
       <c r="AL11">
         <v>0</v>
       </c>
       <c r="AM11">
         <v>0</v>
-      </c>
-      <c r="AN11">
-        <v>1121.074074074074</v>
-      </c>
-      <c r="AP11">
-        <v>-71.30253433086467</v>
       </c>
     </row>
     <row r="12">
@@ -1835,7 +1832,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Malayan Banking Berhad (KLSE:MAYBANK)</t>
+          <t>RHB Bank Berhad (KLSE:RHBBANK)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1844,13 +1841,10 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.0276</v>
+        <v>0.0503</v>
       </c>
       <c r="E12">
-        <v>0.009509999999999999</v>
-      </c>
-      <c r="F12">
-        <v>0.102</v>
+        <v>0.0654</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1859,34 +1853,34 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>0.0009217918269128984</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>0.0006633032056575734</v>
       </c>
       <c r="K12">
-        <v>1748.1</v>
+        <v>643.3</v>
       </c>
       <c r="L12">
-        <v>0.3415725507053812</v>
+        <v>0.3762648417851084</v>
       </c>
       <c r="M12">
-        <v>1471.3</v>
+        <v>284</v>
       </c>
       <c r="N12">
-        <v>0.0614495973804671</v>
+        <v>0.05577157220847571</v>
       </c>
       <c r="O12">
-        <v>0.8416566557977233</v>
+        <v>0.4414736514845329</v>
       </c>
       <c r="P12">
-        <v>1471.3</v>
+        <v>284</v>
       </c>
       <c r="Q12">
-        <v>0.0614495973804671</v>
+        <v>0.05577157220847571</v>
       </c>
       <c r="R12">
-        <v>0.8416566557977233</v>
+        <v>0.4414736514845329</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -1895,61 +1889,67 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>8242.799999999999</v>
+        <v>2702.2</v>
       </c>
       <c r="V12">
-        <v>0.3442647599318386</v>
+        <v>0.5306547268371234</v>
       </c>
       <c r="W12">
-        <v>0.08715921102490974</v>
+        <v>0.1066072286760685</v>
       </c>
       <c r="X12">
-        <v>0.09768539953774726</v>
+        <v>0.0806498068872484</v>
       </c>
       <c r="Y12">
-        <v>-0.01052618851283751</v>
+        <v>0.02595742178882006</v>
       </c>
       <c r="Z12">
-        <v>0.1996590292868094</v>
+        <v>0.3244046281694808</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>0.0002151786297949698</v>
       </c>
       <c r="AB12">
-        <v>0.07682589827495988</v>
+        <v>0.06605814604332103</v>
       </c>
       <c r="AC12">
-        <v>-0.07682589827495988</v>
+        <v>-0.06584296741352605</v>
       </c>
       <c r="AD12">
-        <v>20916.5</v>
+        <v>4508.5</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>3.370062567635087</v>
       </c>
       <c r="AF12">
-        <v>20916.5</v>
+        <v>4511.870062567635</v>
       </c>
       <c r="AG12">
-        <v>12673.7</v>
+        <v>1809.670062567635</v>
       </c>
       <c r="AH12">
-        <v>0.4662648212092368</v>
+        <v>0.469787291551827</v>
       </c>
       <c r="AI12">
-        <v>0.5278012591629972</v>
+        <v>0.4143066670809957</v>
       </c>
       <c r="AJ12">
-        <v>0.3461161376304384</v>
+        <v>0.2621999611934742</v>
       </c>
       <c r="AK12">
-        <v>0.4037920520475233</v>
+        <v>0.2210157155850845</v>
       </c>
       <c r="AL12">
         <v>0</v>
       </c>
       <c r="AM12">
         <v>0</v>
+      </c>
+      <c r="AN12">
+        <v>2003.777777777778</v>
+      </c>
+      <c r="AP12">
+        <v>804.2978055856155</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/malaysia/malaysia_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/malaysia/malaysia_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0441</v>
+        <v>0.04435</v>
       </c>
       <c r="E2">
-        <v>0.0452</v>
+        <v>0.0532</v>
       </c>
       <c r="F2">
-        <v>0.06335</v>
+        <v>0.0767</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,97 +603,103 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>6.557363981563852E-05</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>5.209375715920169E-05</v>
       </c>
       <c r="K2">
-        <v>4101.2</v>
+        <v>9385.799999999999</v>
       </c>
       <c r="L2">
-        <v>0.4136317334167079</v>
+        <v>0.4150364369605207</v>
       </c>
       <c r="M2">
-        <v>2698</v>
+        <v>5809.32</v>
       </c>
       <c r="N2">
-        <v>0.05688250957704966</v>
+        <v>0.06046676228680629</v>
       </c>
       <c r="O2">
-        <v>0.6578562371988687</v>
+        <v>0.6189477721664642</v>
       </c>
       <c r="P2">
-        <v>2698</v>
+        <v>5803.98</v>
       </c>
       <c r="Q2">
-        <v>0.05688250957704966</v>
+        <v>0.06041118047850316</v>
       </c>
       <c r="R2">
-        <v>0.6578562371988687</v>
+        <v>0.6183788275906157</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>5.340000000000003</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.0009192125756542941</v>
       </c>
       <c r="U2">
-        <v>11855.1</v>
+        <v>30038.2</v>
       </c>
       <c r="V2">
-        <v>0.2499436024043296</v>
+        <v>0.3126549577099462</v>
       </c>
       <c r="W2">
-        <v>0.1366887918663523</v>
+        <v>0.1242891127529704</v>
       </c>
       <c r="X2">
-        <v>0.07958764273555594</v>
+        <v>0.08943275694447525</v>
       </c>
       <c r="Y2">
-        <v>0.05710114913079639</v>
+        <v>0.03485635580849519</v>
       </c>
       <c r="Z2">
-        <v>0.2005907403473634</v>
+        <v>0.1955598386011395</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06903533580189314</v>
+        <v>0.0675394756280823</v>
       </c>
       <c r="AC2">
-        <v>-0.06903533580189314</v>
+        <v>-0.06750427846650739</v>
       </c>
       <c r="AD2">
-        <v>30776.1</v>
+        <v>90095</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>3.285457398766123</v>
       </c>
       <c r="AF2">
-        <v>30776.1</v>
+        <v>90098.28545739877</v>
       </c>
       <c r="AG2">
-        <v>18921</v>
+        <v>60060.08545739877</v>
       </c>
       <c r="AH2">
-        <v>0.3935200339610676</v>
+        <v>0.4839495570799198</v>
       </c>
       <c r="AI2">
-        <v>0.4569739678919516</v>
+        <v>0.4956910518974493</v>
       </c>
       <c r="AJ2">
-        <v>0.2851605299606192</v>
+        <v>0.3846684372626871</v>
       </c>
       <c r="AK2">
-        <v>0.3409649952696311</v>
+        <v>0.39584887384311</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
         <v>0</v>
+      </c>
+      <c r="AN2">
+        <v>42100.46728971962</v>
+      </c>
+      <c r="AP2">
+        <v>28065.46049411158</v>
       </c>
     </row>
     <row r="3">
@@ -704,7 +710,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Malayan Banking Berhad (KLSE:MAYBANK)</t>
+          <t>AFFIN Bank Berhad (KLSE:AFFIN)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,13 +719,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0411</v>
+        <v>0.0266</v>
       </c>
       <c r="E3">
-        <v>0.0425</v>
+        <v>-0.0406</v>
       </c>
       <c r="F3">
-        <v>0.0767</v>
+        <v>0.108</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,28 +740,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>2412.2</v>
+        <v>100.5</v>
       </c>
       <c r="L3">
-        <v>0.3635623747155194</v>
+        <v>0.1904130352406215</v>
       </c>
       <c r="M3">
-        <v>1756.3</v>
+        <v>4.28</v>
       </c>
       <c r="N3">
-        <v>0.06355277489298108</v>
+        <v>0.002739550662484798</v>
       </c>
       <c r="O3">
-        <v>0.7280905397562392</v>
+        <v>0.04258706467661692</v>
       </c>
       <c r="P3">
-        <v>1756.3</v>
+        <v>4.28</v>
       </c>
       <c r="Q3">
-        <v>0.06355277489298108</v>
+        <v>0.002739550662484798</v>
       </c>
       <c r="R3">
-        <v>0.7280905397562392</v>
+        <v>0.04258706467661692</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,55 +770,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>8612.799999999999</v>
+        <v>697.9</v>
       </c>
       <c r="V3">
-        <v>0.3116593632057549</v>
+        <v>0.4467131792869487</v>
       </c>
       <c r="W3">
-        <v>0.1243543082205198</v>
+        <v>0.04289372599231754</v>
       </c>
       <c r="X3">
-        <v>0.08613456854020844</v>
+        <v>0.113383256148682</v>
       </c>
       <c r="Y3">
-        <v>0.03821973968031141</v>
+        <v>-0.07048953015636446</v>
       </c>
       <c r="Z3">
-        <v>0.1799299794711308</v>
+        <v>0.1376666058060982</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.06898072299331129</v>
+        <v>0.06699624081412175</v>
       </c>
       <c r="AC3">
-        <v>-0.06898072299331129</v>
+        <v>-0.06699624081412175</v>
       </c>
       <c r="AD3">
-        <v>26440.4</v>
+        <v>3895.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>26440.4</v>
+        <v>3895.3</v>
       </c>
       <c r="AG3">
-        <v>17827.6</v>
+        <v>3197.4</v>
       </c>
       <c r="AH3">
-        <v>0.4889515993320475</v>
+        <v>0.7137386396951041</v>
       </c>
       <c r="AI3">
-        <v>0.5377157999418365</v>
+        <v>0.5822571001494768</v>
       </c>
       <c r="AJ3">
-        <v>0.3921351255639214</v>
+        <v>0.6717650272075971</v>
       </c>
       <c r="AK3">
-        <v>0.4395484098434623</v>
+        <v>0.5336025767260226</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -829,120 +835,1123 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>CIMB Group Holdings Berhad (KLSE:CIMB)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>0.0544</v>
+      </c>
+      <c r="E4">
+        <v>0.09619999999999999</v>
+      </c>
+      <c r="F4">
+        <v>0.08220000000000001</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>1853.9</v>
+      </c>
+      <c r="L4">
+        <v>0.3650415468829992</v>
+      </c>
+      <c r="M4">
+        <v>1813.9</v>
+      </c>
+      <c r="N4">
+        <v>0.09226864168391924</v>
+      </c>
+      <c r="O4">
+        <v>0.9784238632072927</v>
+      </c>
+      <c r="P4">
+        <v>1813.9</v>
+      </c>
+      <c r="Q4">
+        <v>0.09226864168391924</v>
+      </c>
+      <c r="R4">
+        <v>0.9784238632072927</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>6066</v>
+      </c>
+      <c r="V4">
+        <v>0.3085625340176714</v>
+      </c>
+      <c r="W4">
+        <v>0.1276157828074233</v>
+      </c>
+      <c r="X4">
+        <v>0.0957334104742896</v>
+      </c>
+      <c r="Y4">
+        <v>0.03188237233313371</v>
+      </c>
+      <c r="Z4">
+        <v>0.1821043874872707</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0.06733944260034463</v>
+      </c>
+      <c r="AC4">
+        <v>-0.06733944260034463</v>
+      </c>
+      <c r="AD4">
+        <v>29459.6</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>29459.6</v>
+      </c>
+      <c r="AG4">
+        <v>23393.6</v>
+      </c>
+      <c r="AH4">
+        <v>0.5997658723291631</v>
+      </c>
+      <c r="AI4">
+        <v>0.6396515523594256</v>
+      </c>
+      <c r="AJ4">
+        <v>0.5433737878171999</v>
+      </c>
+      <c r="AK4">
+        <v>0.5849906350885353</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>RHB Bank Berhad (KLSE:RHBBANK)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>0.0301</v>
+      </c>
+      <c r="E5">
+        <v>0.0342</v>
+      </c>
+      <c r="F5">
+        <v>0.08900000000000001</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0.0007913065743045761</v>
+      </c>
+      <c r="J5">
+        <v>0.0006022424898918528</v>
+      </c>
+      <c r="K5">
+        <v>696.6</v>
+      </c>
+      <c r="L5">
+        <v>0.3717182497331911</v>
+      </c>
+      <c r="M5">
+        <v>487.9</v>
+      </c>
+      <c r="N5">
+        <v>0.07722380500158278</v>
+      </c>
+      <c r="O5">
+        <v>0.7004019523399367</v>
+      </c>
+      <c r="P5">
+        <v>487.9</v>
+      </c>
+      <c r="Q5">
+        <v>0.07722380500158278</v>
+      </c>
+      <c r="R5">
+        <v>0.7004019523399367</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>1897.4</v>
+      </c>
+      <c r="V5">
+        <v>0.3003165558721114</v>
+      </c>
+      <c r="W5">
+        <v>0.1093426257298926</v>
+      </c>
+      <c r="X5">
+        <v>0.08882572746315795</v>
+      </c>
+      <c r="Y5">
+        <v>0.02051689826673468</v>
+      </c>
+      <c r="Z5">
+        <v>0.246090475344467</v>
+      </c>
+      <c r="AA5">
+        <v>0.0001482061406101214</v>
+      </c>
+      <c r="AB5">
+        <v>0.06756190600671569</v>
+      </c>
+      <c r="AC5">
+        <v>-0.06741369986610557</v>
+      </c>
+      <c r="AD5">
+        <v>7004.7</v>
+      </c>
+      <c r="AE5">
+        <v>3.285457398766123</v>
+      </c>
+      <c r="AF5">
+        <v>7007.985457398766</v>
+      </c>
+      <c r="AG5">
+        <v>5110.585457398765</v>
+      </c>
+      <c r="AH5">
+        <v>0.5258887216860828</v>
+      </c>
+      <c r="AI5">
+        <v>0.4763161840476787</v>
+      </c>
+      <c r="AJ5">
+        <v>0.4471756786042334</v>
+      </c>
+      <c r="AK5">
+        <v>0.3987820418030493</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+      <c r="AN5">
+        <v>3273.22429906542</v>
+      </c>
+      <c r="AP5">
+        <v>2388.124045513442</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>AMMB Holdings Berhad (KLSE:AMBANK)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>0.00796</v>
+      </c>
+      <c r="E6">
+        <v>0.0585</v>
+      </c>
+      <c r="F6">
+        <v>0.047</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>490.2</v>
+      </c>
+      <c r="L6">
+        <v>0.4895635673624288</v>
+      </c>
+      <c r="M6">
+        <v>187.94</v>
+      </c>
+      <c r="N6">
+        <v>0.04632144529613289</v>
+      </c>
+      <c r="O6">
+        <v>0.3833945328437373</v>
+      </c>
+      <c r="P6">
+        <v>182.6</v>
+      </c>
+      <c r="Q6">
+        <v>0.04500529909052818</v>
+      </c>
+      <c r="R6">
+        <v>0.37250101999184</v>
+      </c>
+      <c r="S6">
+        <v>5.340000000000003</v>
+      </c>
+      <c r="T6">
+        <v>0.02841332340108547</v>
+      </c>
+      <c r="U6">
+        <v>1627</v>
+      </c>
+      <c r="V6">
+        <v>0.4010055948537204</v>
+      </c>
+      <c r="W6">
+        <v>0.1242239172854211</v>
+      </c>
+      <c r="X6">
+        <v>0.09095408614629859</v>
+      </c>
+      <c r="Y6">
+        <v>0.03326983113912246</v>
+      </c>
+      <c r="Z6">
+        <v>0.1639916145304465</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0.06748507894134685</v>
+      </c>
+      <c r="AC6">
+        <v>-0.06748507894134685</v>
+      </c>
+      <c r="AD6">
+        <v>4987.1</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>4987.1</v>
+      </c>
+      <c r="AG6">
+        <v>3360.1</v>
+      </c>
+      <c r="AH6">
+        <v>0.5514019724912652</v>
+      </c>
+      <c r="AI6">
+        <v>0.5072572852565733</v>
+      </c>
+      <c r="AJ6">
+        <v>0.4530023997627201</v>
+      </c>
+      <c r="AK6">
+        <v>0.4095435431775246</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Hong Leong Financial Group Berhad (KLSE:HLFG)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>0.0601</v>
+      </c>
+      <c r="E7">
+        <v>0.117</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>801.4</v>
+      </c>
+      <c r="L7">
+        <v>0.4704984441965596</v>
+      </c>
+      <c r="M7">
+        <v>138.1</v>
+      </c>
+      <c r="N7">
+        <v>0.02942680588109951</v>
+      </c>
+      <c r="O7">
+        <v>0.1723234339905166</v>
+      </c>
+      <c r="P7">
+        <v>138.1</v>
+      </c>
+      <c r="Q7">
+        <v>0.02942680588109951</v>
+      </c>
+      <c r="R7">
+        <v>0.1723234339905166</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>3464.2</v>
+      </c>
+      <c r="V7">
+        <v>0.7381632218197315</v>
+      </c>
+      <c r="W7">
+        <v>0.1368253914053029</v>
+      </c>
+      <c r="X7">
+        <v>0.09076663571498886</v>
+      </c>
+      <c r="Y7">
+        <v>0.04605875569031409</v>
+      </c>
+      <c r="Z7">
+        <v>0.2182738514769013</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0.06749151168356586</v>
+      </c>
+      <c r="AC7">
+        <v>-0.06749151168356586</v>
+      </c>
+      <c r="AD7">
+        <v>5718.9</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>5718.9</v>
+      </c>
+      <c r="AG7">
+        <v>2254.7</v>
+      </c>
+      <c r="AH7">
+        <v>0.5492657440044564</v>
+      </c>
+      <c r="AI7">
+        <v>0.349807629964462</v>
+      </c>
+      <c r="AJ7">
+        <v>0.3245246628380615</v>
+      </c>
+      <c r="AK7">
+        <v>0.174993208894408</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Bank Islam Malaysia Berhad (KLSE:BIMB)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>0.0416</v>
+      </c>
+      <c r="E8">
+        <v>-0.0203</v>
+      </c>
+      <c r="F8">
+        <v>0.05400000000000001</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>134.6</v>
+      </c>
+      <c r="L8">
+        <v>0.2345765074939003</v>
+      </c>
+      <c r="M8">
+        <v>82.3</v>
+      </c>
+      <c r="N8">
+        <v>0.06573482428115016</v>
+      </c>
+      <c r="O8">
+        <v>0.611441307578009</v>
+      </c>
+      <c r="P8">
+        <v>82.3</v>
+      </c>
+      <c r="Q8">
+        <v>0.06573482428115016</v>
+      </c>
+      <c r="R8">
+        <v>0.611441307578009</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>747.1</v>
+      </c>
+      <c r="V8">
+        <v>0.5967252396166134</v>
+      </c>
+      <c r="W8">
+        <v>0.08477138178611916</v>
+      </c>
+      <c r="X8">
+        <v>0.09003978642579256</v>
+      </c>
+      <c r="Y8">
+        <v>-0.005268404639673402</v>
+      </c>
+      <c r="Z8">
+        <v>0.2704052780395853</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0.0675170452494489</v>
+      </c>
+      <c r="AC8">
+        <v>-0.0675170452494489</v>
+      </c>
+      <c r="AD8">
+        <v>1474.4</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>1474.4</v>
+      </c>
+      <c r="AG8">
+        <v>727.3000000000001</v>
+      </c>
+      <c r="AH8">
+        <v>0.5407863849765259</v>
+      </c>
+      <c r="AI8">
+        <v>0.4386789645938709</v>
+      </c>
+      <c r="AJ8">
+        <v>0.3674531399989895</v>
+      </c>
+      <c r="AK8">
+        <v>0.278243238073377</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Hong Leong Bank Berhad (KLSE:HLBANK)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>0.0507</v>
+      </c>
+      <c r="E9">
+        <v>0.09970000000000001</v>
+      </c>
+      <c r="F9">
+        <v>0.081</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>1032.5</v>
+      </c>
+      <c r="L9">
+        <v>0.705934636947901</v>
+      </c>
+      <c r="M9">
+        <v>313.2</v>
+      </c>
+      <c r="N9">
+        <v>0.03322653879612145</v>
+      </c>
+      <c r="O9">
+        <v>0.3033414043583535</v>
+      </c>
+      <c r="P9">
+        <v>313.2</v>
+      </c>
+      <c r="Q9">
+        <v>0.03322653879612145</v>
+      </c>
+      <c r="R9">
+        <v>0.3033414043583535</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>2910.4</v>
+      </c>
+      <c r="V9">
+        <v>0.3087564448027837</v>
+      </c>
+      <c r="W9">
+        <v>0.1417860232625204</v>
+      </c>
+      <c r="X9">
+        <v>0.07864037555507869</v>
+      </c>
+      <c r="Y9">
+        <v>0.06314564770744174</v>
+      </c>
+      <c r="Z9">
+        <v>0.1605682354620206</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0.06809577932344638</v>
+      </c>
+      <c r="AC9">
+        <v>-0.06809577932344638</v>
+      </c>
+      <c r="AD9">
+        <v>5044.4</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>5044.4</v>
+      </c>
+      <c r="AG9">
+        <v>2134</v>
+      </c>
+      <c r="AH9">
+        <v>0.3485964645557199</v>
+      </c>
+      <c r="AI9">
+        <v>0.3633220734509258</v>
+      </c>
+      <c r="AJ9">
+        <v>0.1845988823722773</v>
+      </c>
+      <c r="AK9">
+        <v>0.1944649480120652</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Malayan Banking Berhad (KLSE:MAYBANK)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D10">
+        <v>0.0411</v>
+      </c>
+      <c r="E10">
+        <v>0.0425</v>
+      </c>
+      <c r="F10">
+        <v>0.0767</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>2412.2</v>
+      </c>
+      <c r="L10">
+        <v>0.3635623747155194</v>
+      </c>
+      <c r="M10">
+        <v>1756.3</v>
+      </c>
+      <c r="N10">
+        <v>0.06355277489298108</v>
+      </c>
+      <c r="O10">
+        <v>0.7280905397562392</v>
+      </c>
+      <c r="P10">
+        <v>1756.3</v>
+      </c>
+      <c r="Q10">
+        <v>0.06355277489298108</v>
+      </c>
+      <c r="R10">
+        <v>0.7280905397562392</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>8612.799999999999</v>
+      </c>
+      <c r="V10">
+        <v>0.3116593632057549</v>
+      </c>
+      <c r="W10">
+        <v>0.1243543082205198</v>
+      </c>
+      <c r="X10">
+        <v>0.08612091346479375</v>
+      </c>
+      <c r="Y10">
+        <v>0.0382333947557261</v>
+      </c>
+      <c r="Z10">
+        <v>0.1799299794711308</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0.06897374458885963</v>
+      </c>
+      <c r="AC10">
+        <v>-0.06897374458885963</v>
+      </c>
+      <c r="AD10">
+        <v>26440.4</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>26440.4</v>
+      </c>
+      <c r="AG10">
+        <v>17827.6</v>
+      </c>
+      <c r="AH10">
+        <v>0.4889515993320475</v>
+      </c>
+      <c r="AI10">
+        <v>0.5377157999418365</v>
+      </c>
+      <c r="AJ10">
+        <v>0.3921351255639214</v>
+      </c>
+      <c r="AK10">
+        <v>0.4395484098434623</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>Public Bank Berhad (KLSE:PBBANK)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D4">
+      <c r="D11">
         <v>0.0471</v>
       </c>
-      <c r="E4">
+      <c r="E11">
         <v>0.0479</v>
       </c>
-      <c r="F4">
+      <c r="F11">
         <v>0.05</v>
       </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
         <v>1689</v>
       </c>
-      <c r="L4">
+      <c r="L11">
         <v>0.5149076275836839</v>
       </c>
-      <c r="M4">
+      <c r="M11">
         <v>941.7</v>
       </c>
-      <c r="N4">
+      <c r="N11">
         <v>0.0475706968144758</v>
       </c>
-      <c r="O4">
+      <c r="O11">
         <v>0.5575488454706927</v>
       </c>
-      <c r="P4">
+      <c r="P11">
         <v>941.7</v>
       </c>
-      <c r="Q4">
+      <c r="Q11">
         <v>0.0475706968144758</v>
       </c>
-      <c r="R4">
+      <c r="R11">
         <v>0.5575488454706927</v>
       </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
         <v>3242.3</v>
       </c>
-      <c r="V4">
+      <c r="V11">
         <v>0.1637872680063448</v>
       </c>
-      <c r="W4">
+      <c r="W11">
         <v>0.1490232755121848</v>
       </c>
-      <c r="X4">
-        <v>0.07304071693090344</v>
-      </c>
-      <c r="Y4">
-        <v>0.07598255858128136</v>
-      </c>
-      <c r="Z4">
+      <c r="X11">
+        <v>0.07303149471637371</v>
+      </c>
+      <c r="Y11">
+        <v>0.07599178079581109</v>
+      </c>
+      <c r="Z11">
         <v>0.2612747518837717</v>
       </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0.06908994861047499</v>
-      </c>
-      <c r="AC4">
-        <v>-0.06908994861047499</v>
-      </c>
-      <c r="AD4">
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>0.0690823833487056</v>
+      </c>
+      <c r="AC11">
+        <v>-0.0690823833487056</v>
+      </c>
+      <c r="AD11">
         <v>4335.7</v>
       </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
         <v>4335.7</v>
       </c>
-      <c r="AG4">
+      <c r="AG11">
         <v>1093.4</v>
       </c>
-      <c r="AH4">
+      <c r="AH11">
         <v>0.1796697262913619</v>
       </c>
-      <c r="AI4">
+      <c r="AI11">
         <v>0.2385411451427439</v>
       </c>
-      <c r="AJ4">
+      <c r="AJ11">
         <v>0.05234283744710184</v>
       </c>
-      <c r="AK4">
+      <c r="AK11">
         <v>0.0732174425456688</v>
       </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Alliance Bank Malaysia Berhad (KLSE:ABMB)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D12">
+        <v>0.0706</v>
+      </c>
+      <c r="E12">
+        <v>0.0975</v>
+      </c>
+      <c r="F12">
+        <v>0.0745</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>174.9</v>
+      </c>
+      <c r="L12">
+        <v>0.3659761456371626</v>
+      </c>
+      <c r="M12">
+        <v>83.7</v>
+      </c>
+      <c r="N12">
+        <v>0.04994629430719657</v>
+      </c>
+      <c r="O12">
+        <v>0.4785591766723842</v>
+      </c>
+      <c r="P12">
+        <v>83.7</v>
+      </c>
+      <c r="Q12">
+        <v>0.04994629430719657</v>
+      </c>
+      <c r="R12">
+        <v>0.4785591766723842</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>773.1</v>
+      </c>
+      <c r="V12">
+        <v>0.4613319011815253</v>
+      </c>
+      <c r="W12">
+        <v>0.1187372708757637</v>
+      </c>
+      <c r="X12">
+        <v>0.08750955786307241</v>
+      </c>
+      <c r="Y12">
+        <v>0.03122771301269134</v>
+      </c>
+      <c r="Z12">
+        <v>0.2758919293384135</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0.06993319259323466</v>
+      </c>
+      <c r="AC12">
+        <v>-0.06993319259323466</v>
+      </c>
+      <c r="AD12">
+        <v>1734.5</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>1734.5</v>
+      </c>
+      <c r="AG12">
+        <v>961.4</v>
+      </c>
+      <c r="AH12">
+        <v>0.5086062809723485</v>
+      </c>
+      <c r="AI12">
+        <v>0.4911510689508707</v>
+      </c>
+      <c r="AJ12">
+        <v>0.3645533141210375</v>
+      </c>
+      <c r="AK12">
+        <v>0.3485353828306264</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
         <v>0</v>
       </c>
     </row>
